--- a/rmonize/data_dictionary/DD_DONALD_P2.xlsx
+++ b/rmonize/data_dictionary/DD_DONALD_P2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="136">
   <si>
     <t>index</t>
   </si>
@@ -43,9 +43,6 @@
     <t>AGE_BASE</t>
   </si>
   <si>
-    <t>EDU_LEVEL_P</t>
-  </si>
-  <si>
     <t>EMPLOY_P</t>
   </si>
   <si>
@@ -352,9 +349,6 @@
     <t>HDL measured from blood samples [mg/dl]</t>
   </si>
   <si>
-    <t>parental education status</t>
-  </si>
-  <si>
     <t>variable</t>
   </si>
   <si>
@@ -364,61 +358,76 @@
     <t>female</t>
   </si>
   <si>
-    <t>Early Childhood Education</t>
-  </si>
-  <si>
-    <t>Primary Education</t>
-  </si>
-  <si>
-    <t>Lower Secondary Education</t>
-  </si>
-  <si>
-    <t>Upper Secondary Education</t>
-  </si>
-  <si>
-    <t>Post-secondary non-tertiary education</t>
-  </si>
-  <si>
-    <t>Short-Cycle Tertiary Education</t>
-  </si>
-  <si>
-    <t>Bachelor's or equivalent level</t>
-  </si>
-  <si>
-    <t>Master's or equivalent level</t>
-  </si>
-  <si>
-    <t>Doctoral or equivalent level</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>employed-full time</t>
-  </si>
-  <si>
-    <t>employed-part time</t>
-  </si>
-  <si>
-    <t>retired</t>
-  </si>
-  <si>
-    <t>unemployed</t>
-  </si>
-  <si>
-    <t>student</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>housewife/-men</t>
+    <t>m_schulab</t>
+  </si>
+  <si>
+    <t>Schuldbildung der Mutter</t>
+  </si>
+  <si>
+    <t>v_schulab</t>
+  </si>
+  <si>
+    <t>Schuldbildung des Vaters</t>
+  </si>
+  <si>
+    <t>b_berufsab</t>
+  </si>
+  <si>
+    <t>Berufsabschluss der Mutter</t>
+  </si>
+  <si>
+    <t>v_berufsab</t>
+  </si>
+  <si>
+    <t>Berufsabschluss des Vaters</t>
+  </si>
+  <si>
+    <t>Volks-/Hauptschulabschluss</t>
+  </si>
+  <si>
+    <t>Mittlere Reife, Realschulabschluss (Fachschulreife)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fachhochschulreife, Abschluss einer Fachoberschule etc.       </t>
+  </si>
+  <si>
+    <t>Abitur (Hochschulreife)</t>
+  </si>
+  <si>
+    <t>keinen dieser Abschlüsse</t>
+  </si>
+  <si>
+    <t>m_berufsab</t>
+  </si>
+  <si>
+    <t>Lehre (beruflich-betriebliche Ausbildung)</t>
+  </si>
+  <si>
+    <t>Berufsschule, Handelsschule (berufl.-schulische Ausbildung)</t>
+  </si>
+  <si>
+    <t>Fachschule (z.B. Meister-Technikerschule, Berufs/Fachakademie)</t>
+  </si>
+  <si>
+    <t>Fachhochschule, Ingenieurschule</t>
+  </si>
+  <si>
+    <t>Universität, Hochschule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anderer Abschluss (bis 3/2016 berufl. Praktikum)                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">kein beruflicher Abschluss     </t>
+  </si>
+  <si>
+    <t>noch in beruflicher Ausbildung (Auszubildener / Student)</t>
   </si>
 </sst>
 </file>
@@ -757,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.90625" style="1" customWidth="1"/>
@@ -789,7 +798,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -800,10 +809,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -814,10 +823,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -825,13 +834,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -839,13 +848,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -853,13 +862,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -867,13 +876,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -881,13 +890,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -895,13 +904,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -909,13 +918,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -923,13 +932,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -937,13 +946,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -951,13 +960,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -965,13 +974,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -979,13 +988,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -993,13 +1002,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1007,13 +1016,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1021,13 +1030,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1035,13 +1044,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1049,13 +1058,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1063,13 +1072,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1077,13 +1086,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1091,13 +1100,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1105,13 +1114,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1119,13 +1128,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1133,13 +1142,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1147,13 +1156,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1161,13 +1170,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1175,13 +1184,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1189,13 +1198,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1203,13 +1212,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1217,13 +1226,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1231,13 +1240,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1245,13 +1254,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -1259,13 +1268,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1273,13 +1282,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1287,13 +1296,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1301,13 +1310,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -1315,13 +1324,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -1329,13 +1338,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -1343,13 +1352,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -1357,13 +1366,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -1371,13 +1380,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1385,13 +1394,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -1399,13 +1408,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -1413,13 +1422,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -1427,13 +1436,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1441,13 +1450,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1455,13 +1464,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -1469,13 +1478,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -1483,13 +1492,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -1497,13 +1506,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -1511,13 +1520,55 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" t="s">
-        <v>58</v>
+      <c r="B57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1528,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
@@ -1536,7 +1587,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1553,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1564,216 +1615,315 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="B20">
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/rmonize/data_dictionary/DD_DONALD_P2.xlsx
+++ b/rmonize/data_dictionary/DD_DONALD_P2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="143">
   <si>
     <t>index</t>
   </si>
@@ -428,6 +428,27 @@
   </si>
   <si>
     <t>noch in beruflicher Ausbildung (Auszubildener / Student)</t>
+  </si>
+  <si>
+    <t>employed-full time</t>
+  </si>
+  <si>
+    <t>employed-part time</t>
+  </si>
+  <si>
+    <t>housewife/-men</t>
+  </si>
+  <si>
+    <t>retired</t>
+  </si>
+  <si>
+    <t>unemployed</t>
+  </si>
+  <si>
+    <t>student</t>
+  </si>
+  <si>
+    <t>other</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
@@ -1905,24 +1926,101 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B30">
+      <c r="B37">
         <v>0</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B31">
+      <c r="B38">
         <v>1</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C38" t="s">
         <v>113</v>
       </c>
     </row>

--- a/rmonize/data_dictionary/DD_DONALD_P2.xlsx
+++ b/rmonize/data_dictionary/DD_DONALD_P2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78275A53-95C3-4D87-9C8E-A8571778C07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14895" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="142">
   <si>
     <t>index</t>
   </si>
@@ -376,15 +377,9 @@
     <t>Schuldbildung des Vaters</t>
   </si>
   <si>
-    <t>b_berufsab</t>
-  </si>
-  <si>
     <t>Berufsabschluss der Mutter</t>
   </si>
   <si>
-    <t>v_berufsab</t>
-  </si>
-  <si>
     <t>Berufsabschluss des Vaters</t>
   </si>
   <si>
@@ -403,9 +398,6 @@
     <t>keinen dieser Abschlüsse</t>
   </si>
   <si>
-    <t>m_berufsab</t>
-  </si>
-  <si>
     <t>Lehre (beruflich-betriebliche Ausbildung)</t>
   </si>
   <si>
@@ -449,12 +441,18 @@
   </si>
   <si>
     <t>other</t>
+  </si>
+  <si>
+    <t>m_berufab</t>
+  </si>
+  <si>
+    <t>v_berufab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -509,7 +507,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -786,15 +784,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -808,7 +806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -822,7 +820,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -836,7 +834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -850,7 +848,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -864,7 +862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -878,35 +876,35 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -920,7 +918,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -934,7 +932,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -948,7 +946,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -962,7 +960,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -976,7 +974,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -990,7 +988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1004,7 +1002,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1018,7 +1016,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1032,7 +1030,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1046,7 +1044,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1060,7 +1058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1074,7 +1072,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1088,7 +1086,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1102,7 +1100,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1116,7 +1114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1130,7 +1128,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1144,7 +1142,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1158,7 +1156,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1172,7 +1170,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1186,7 +1184,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1200,7 +1198,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1214,7 +1212,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1228,7 +1226,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1242,7 +1240,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1256,7 +1254,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1270,7 +1268,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1284,7 +1282,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1298,7 +1296,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1312,7 +1310,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1326,7 +1324,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1340,7 +1338,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1354,7 +1352,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1368,7 +1366,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1382,7 +1380,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1396,7 +1394,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1410,7 +1408,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1424,7 +1422,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1438,7 +1436,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1452,7 +1450,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1466,7 +1464,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1480,7 +1478,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1494,7 +1492,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1508,7 +1506,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1522,7 +1520,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1536,7 +1534,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1550,7 +1548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1564,7 +1562,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1578,7 +1576,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1599,14 +1597,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>109</v>
       </c>
@@ -1617,7 +1615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1628,7 +1626,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1639,7 +1637,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>114</v>
       </c>
@@ -1647,10 +1645,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>114</v>
       </c>
@@ -1658,10 +1656,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>114</v>
       </c>
@@ -1669,10 +1667,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>114</v>
       </c>
@@ -1680,10 +1678,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>114</v>
       </c>
@@ -1691,10 +1689,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>116</v>
       </c>
@@ -1702,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>116</v>
       </c>
@@ -1713,10 +1711,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>116</v>
       </c>
@@ -1724,10 +1722,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>116</v>
       </c>
@@ -1735,10 +1733,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>116</v>
       </c>
@@ -1746,186 +1744,186 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B20">
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B21">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B28">
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B29">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1933,10 +1931,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1944,10 +1942,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1955,10 +1953,10 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1966,10 +1964,10 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1977,10 +1975,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1988,10 +1986,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1999,10 +1997,10 @@
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
@@ -2013,7 +2011,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>9</v>
       </c>
